--- a/Assets/Data/Excel/WeaponData.xlsx
+++ b/Assets/Data/Excel/WeaponData.xlsx
@@ -1,37 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -79,44 +135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -143,15 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -178,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -190,150 +244,1097 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>coin</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>exclude_ids</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_unique</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>weapon_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>min_grade</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_grade</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>attack_speed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>crit_damage</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>knockback</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>piercing</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>bounce</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>icon_path</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sprite_path</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>sprite_x</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>sprite_y</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>recoil_distance</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>recoil_duration</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>muzzle_x</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>muzzle_y</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>projectile_path</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>fly_speed</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>max_life_time</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>melee_attack_type</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>auto_hitbox_from_sprite</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>melee_thrust_distance</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>melee_windup</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>melee_active</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>melee_return</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>deal_damage_on_return</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string[]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>武器ID</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>基础品阶(兼容字段)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>基础价格</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>互斥ID</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>是否唯一(购买后不再刷取)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>类型 Melee/Ranged</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>最低可刷品阶</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>最高可刷品阶(=min即固定品阶,4=神话)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>基础伤害</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>攻击间隔秒</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>射程(远程侦测/近战参考)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>暴击概率0~1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>暴击倍率</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>击退力度</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>远程可命中敌人数</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>远程弹射次数(预留)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>图标Resources路径</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>世界贴图Resources路径</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>贴图本地偏移X</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>贴图本地偏移Y</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>后坐力距离</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>后坐力时长</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>枪口本地偏移X</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>枪口本地偏移Y</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>子弹Resources路径(远程)</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>子弹飞行速度</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>子弹存活秒</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>近战类型 Thrust/Sweep</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>命中盒按贴图自动包裹</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>戳刺位移</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>近战蓄力时长</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>近战命中窗口时长</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>近战收回时长</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>收回是否造成伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>201</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>手枪</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gun</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Weapons/Icons/pistol_icon</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Weapons/Sprites/pistol</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Weapons/Projectiles/bullet</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>202</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>长矛</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Blade</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Weapons/Icons/spear_icon</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Weapons/Sprites/spear</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Thrust</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>203</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Blade</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>25</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Weapons/Icons/sword_icon</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Weapons/Sprites/sword</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Sweep</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>